--- a/resources/templates/standard/L1100-08.xlsx
+++ b/resources/templates/standard/L1100-08.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>NO</t>
   </si>
@@ -709,7 +712,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -816,22 +821,22 @@
     </row>
     <row r="3" ht="26.25" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -844,14 +849,14 @@
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
       <c r="U3" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
@@ -859,27 +864,27 @@
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
       <c r="AF3" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL3" s="7"/>
       <c r="AM3" s="7"/>
       <c r="AN3" s="7"/>
       <c r="AO3" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP3" s="7"/>
       <c r="AQ3" s="7"/>
       <c r="AR3" s="7"/>
       <c r="AS3" s="7"/>
       <c r="AT3" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU3" s="7"/>
       <c r="AV3" s="7"/>
